--- a/threagile/output/linddun/risks.xlsx
+++ b/threagile/output/linddun/risks.xlsx
@@ -19,64 +19,64 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="115">
   <si>
+    <t>RAA %</t>
+  </si>
+  <si>
+    <t>Identified Risk</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Check</t>
+  </si>
+  <si>
+    <t>Ticket</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Likelihood</t>
+  </si>
+  <si>
+    <t>Communication Link</t>
+  </si>
+  <si>
+    <t>Checked by</t>
+  </si>
+  <si>
+    <t>STRIDE</t>
+  </si>
+  <si>
+    <t>CWE</t>
+  </si>
+  <si>
     <t>Risk Category</t>
   </si>
   <si>
+    <t>Mitigation</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <t>Impact</t>
+  </si>
+  <si>
     <t>Technical Asset</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Ticket</t>
-  </si>
-  <si>
-    <t>Communication Link</t>
-  </si>
-  <si>
-    <t>RAA %</t>
-  </si>
-  <si>
-    <t>Justification</t>
-  </si>
-  <si>
-    <t>Checked by</t>
-  </si>
-  <si>
-    <t>Function</t>
-  </si>
-  <si>
-    <t>Identified Risk</t>
-  </si>
-  <si>
-    <t>Mitigation</t>
-  </si>
-  <si>
-    <t>Check</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Severity</t>
-  </si>
-  <si>
-    <t>Likelihood</t>
-  </si>
-  <si>
-    <t>Impact</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>STRIDE</t>
-  </si>
-  <si>
-    <t>CWE</t>
   </si>
   <si>
     <t>Elevated</t>
@@ -927,58 +927,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E1" s="24" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F1" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="I1" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="K1" s="24" t="s">
         <v>1</v>
-      </c>
-      <c r="I1" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="24" t="s">
-        <v>10</v>
       </c>
       <c r="L1" s="24" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="24" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" s="24" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O1" s="24" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="P1" s="24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q1" s="24" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="R1" s="24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S1" s="24" t="s">
         <v>8</v>

--- a/threagile/output/linddun/risks.xlsx
+++ b/threagile/output/linddun/risks.xlsx
@@ -10,75 +10,75 @@
     <sheet name="VaultNote Threat Model" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'VaultNote Threat Model'!$A$1:$T$13</definedName>
+    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'VaultNote Threat Model'!$A$1:$T$29</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
+  <si>
+    <t>Mitigation</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Checked by</t>
+  </si>
+  <si>
+    <t>CWE</t>
+  </si>
+  <si>
+    <t>Technical Asset</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Ticket</t>
+  </si>
+  <si>
+    <t>Likelihood</t>
+  </si>
+  <si>
+    <t>Impact</t>
+  </si>
+  <si>
+    <t>Identified Risk</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>Communication Link</t>
+  </si>
   <si>
     <t>RAA %</t>
   </si>
   <si>
-    <t>Identified Risk</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
     <t>Check</t>
   </si>
   <si>
-    <t>Ticket</t>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>STRIDE</t>
   </si>
   <si>
     <t>Severity</t>
   </si>
   <si>
-    <t>Likelihood</t>
-  </si>
-  <si>
-    <t>Communication Link</t>
-  </si>
-  <si>
-    <t>Checked by</t>
-  </si>
-  <si>
-    <t>STRIDE</t>
-  </si>
-  <si>
-    <t>CWE</t>
+    <t>Function</t>
   </si>
   <si>
     <t>Risk Category</t>
   </si>
   <si>
-    <t>Mitigation</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Justification</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Function</t>
-  </si>
-  <si>
-    <t>Impact</t>
-  </si>
-  <si>
-    <t>Technical Asset</t>
-  </si>
-  <si>
     <t>Elevated</t>
   </si>
   <si>
@@ -106,7 +106,7 @@
     <t/>
   </si>
   <si>
-    <t>82</t>
+    <t>44</t>
   </si>
   <si>
     <t>Data Disclosure: API Server processes personal data and has an unencrypted outgoing communication link</t>
@@ -143,7 +143,7 @@
     <t>Nginx Reverse Proxy</t>
   </si>
   <si>
-    <t>2</t>
+    <t>1</t>
   </si>
   <si>
     <t>Data Disclosure: Nginx Reverse Proxy processes personal data and has an unencrypted outgoing communication link</t>
@@ -177,7 +177,13 @@
     <t>Detectability - PII Flows Without Audit Logging</t>
   </si>
   <si>
-    <t>Detectability: Nginx Reverse Proxy processes PII and has communication links without audit logging</t>
+    <t>ECS Container Platform</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>Detectability: ECS Container Platform processes PII and has communication links without audit logging</t>
   </si>
   <si>
     <t>Enable audit logging on all links carrying personal data</t>
@@ -190,6 +196,51 @@
     <t>Are all communication links that carry personal data audit-logged?</t>
   </si>
   <si>
+    <t>detecting-no-audit-logging@ecs-platform</t>
+  </si>
+  <si>
+    <t>Unchecked</t>
+  </si>
+  <si>
+    <t>LLM Note Summarizer</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Detectability: LLM Note Summarizer processes PII and has communication links without audit logging</t>
+  </si>
+  <si>
+    <t>detecting-no-audit-logging@llm-summarizer</t>
+  </si>
+  <si>
+    <t>Lambda Email Notifier</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Detectability: Lambda Email Notifier processes PII and has communication links without audit logging</t>
+  </si>
+  <si>
+    <t>detecting-no-audit-logging@lambda-notifier</t>
+  </si>
+  <si>
+    <t>Note RAG Pipeline</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Detectability: Note RAG Pipeline processes PII and has communication links without audit logging</t>
+  </si>
+  <si>
+    <t>detecting-no-audit-logging@rag-pipeline</t>
+  </si>
+  <si>
+    <t>Detectability: Nginx Reverse Proxy processes PII and has communication links without audit logging</t>
+  </si>
+  <si>
     <t>detecting-no-audit-logging@nginx-proxy</t>
   </si>
   <si>
@@ -216,6 +267,88 @@
     <t>VAULT-116</t>
   </si>
   <si>
+    <t>CWE-312</t>
+  </si>
+  <si>
+    <t>Identifiability - Personal Data Stored Without Encryption at Rest</t>
+  </si>
+  <si>
+    <t>AWS RDS PostgreSQL</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>Identifiability: datastore AWS RDS PostgreSQL stores personal data without encryption at rest</t>
+  </si>
+  <si>
+    <t>Enable encryption at rest on all datastores holding personal data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable disk-level or database-level encryption on every datastore asset that stores PII data assets. Use full-disk encryption (LUKS, AWS EBS encryption, Azure SSE) or database-level TDE (pgcrypto, SQL Server TDE).
+</t>
+  </si>
+  <si>
+    <t>Is every datastore that holds personal data encrypted at rest?</t>
+  </si>
+  <si>
+    <t>identifying-pii-stored-unencrypted@rds-postgresql</t>
+  </si>
+  <si>
+    <t>AWS S3 Notes Bucket</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>Identifiability: datastore AWS S3 Notes Bucket stores personal data without encryption at rest</t>
+  </si>
+  <si>
+    <t>identifying-pii-stored-unencrypted@s3-notes-bucket</t>
+  </si>
+  <si>
+    <t>MinIO Object Storage</t>
+  </si>
+  <si>
+    <t>Identifiability: datastore MinIO Object Storage stores personal data without encryption at rest</t>
+  </si>
+  <si>
+    <t>identifying-pii-stored-unencrypted@minio-storage</t>
+  </si>
+  <si>
+    <t>PostgreSQL Database</t>
+  </si>
+  <si>
+    <t>Identifiability: datastore PostgreSQL Database stores personal data without encryption at rest</t>
+  </si>
+  <si>
+    <t>identifying-pii-stored-unencrypted@postgresql-db</t>
+  </si>
+  <si>
+    <t>Redis Cache</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Identifiability: datastore Redis Cache stores personal data without encryption at rest</t>
+  </si>
+  <si>
+    <t>identifying-pii-stored-unencrypted@redis-cache</t>
+  </si>
+  <si>
+    <t>VaultNote Vector Store</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Identifiability: datastore VaultNote Vector Store stores personal data without encryption at rest</t>
+  </si>
+  <si>
+    <t>identifying-pii-stored-unencrypted@vector-store</t>
+  </si>
+  <si>
     <t>Development</t>
   </si>
   <si>
@@ -228,7 +361,7 @@
     <t>Browser SPA</t>
   </si>
   <si>
-    <t>54</t>
+    <t>29</t>
   </si>
   <si>
     <t>PII in Client-Side Storage: browser asset Browser SPA processes personal data that may be stored in JavaScript-accessible browser storage</t>
@@ -248,9 +381,6 @@
     <t>pii-client-side-storage@browser-spa</t>
   </si>
   <si>
-    <t>Unchecked</t>
-  </si>
-  <si>
     <t>CWE-359</t>
   </si>
   <si>
@@ -289,7 +419,13 @@
     <t>Linkability - Same PII Data Asset Processed Across Multiple Trust Boundaries</t>
   </si>
   <si>
-    <t>Linkability: API Server processes a PII data asset also flowing into another trust boundary</t>
+    <t>AWS API Gateway</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Linkability: AWS API Gateway processes a PII data asset also flowing into another trust boundary</t>
   </si>
   <si>
     <t>Apply data minimisation and per-context pseudonymisation</t>
@@ -302,6 +438,42 @@
     <t>Does each PII data asset appear in assets across more than one trust boundary?</t>
   </si>
   <si>
+    <t>linking-pii-multi-boundary@aws-api-gateway</t>
+  </si>
+  <si>
+    <t>Linkability: AWS RDS PostgreSQL processes a PII data asset also flowing into another trust boundary</t>
+  </si>
+  <si>
+    <t>linking-pii-multi-boundary@rds-postgresql</t>
+  </si>
+  <si>
+    <t>Linkability: AWS S3 Notes Bucket processes a PII data asset also flowing into another trust boundary</t>
+  </si>
+  <si>
+    <t>linking-pii-multi-boundary@s3-notes-bucket</t>
+  </si>
+  <si>
+    <t>Linkability: ECS Container Platform processes a PII data asset also flowing into another trust boundary</t>
+  </si>
+  <si>
+    <t>linking-pii-multi-boundary@ecs-platform</t>
+  </si>
+  <si>
+    <t>Linkability: Note RAG Pipeline processes a PII data asset also flowing into another trust boundary</t>
+  </si>
+  <si>
+    <t>linking-pii-multi-boundary@rag-pipeline</t>
+  </si>
+  <si>
+    <t>Linkability: VaultNote Vector Store processes a PII data asset also flowing into another trust boundary</t>
+  </si>
+  <si>
+    <t>linking-pii-multi-boundary@vector-store</t>
+  </si>
+  <si>
+    <t>Linkability: API Server processes a PII data asset also flowing into another trust boundary</t>
+  </si>
+  <si>
     <t>linking-pii-multi-boundary@api-server</t>
   </si>
   <si>
@@ -322,12 +494,6 @@
 </t>
   </si>
   <si>
-    <t>MinIO Object Storage</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
     <t>Linkability: MinIO Object Storage processes a PII data asset also flowing into another trust boundary</t>
   </si>
   <si>
@@ -348,12 +514,6 @@
 </t>
   </si>
   <si>
-    <t>PostgreSQL Database</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
     <t>Linkability: PostgreSQL Database processes a PII data asset also flowing into another trust boundary</t>
   </si>
   <si>
@@ -362,12 +522,6 @@
   <si>
     <t xml:space="preserve">PostgreSQL stores credentials and note content that originate from multiple trust boundaries (Internet → DMZ → App Network → Data Tier). This is inherent to the data flow by design. Risk is accepted; mitigated by parameterized queries and authentication-only access via the API.
 </t>
-  </si>
-  <si>
-    <t>Redis Cache</t>
-  </si>
-  <si>
-    <t>40</t>
   </si>
   <si>
     <t>Linkability: Redis Cache processes a PII data asset also flowing into another trust boundary</t>
@@ -910,14 +1064,14 @@
     <col customWidth="true" max="5" min="5" width="17"/>
     <col customWidth="true" max="6" min="6" width="12.714285714285714"/>
     <col customWidth="true" max="7" min="7" width="71.85714285714285"/>
-    <col customWidth="true" max="8" min="8" width="23.857142857142858"/>
+    <col customWidth="true" max="8" min="8" width="25.57142857142857"/>
     <col customWidth="true" max="9" min="9" width="25"/>
     <col customWidth="true" max="10" min="10" width="12"/>
     <col customWidth="true" max="11" min="11" width="75"/>
     <col customWidth="true" max="12" min="12" width="56.42857142857143"/>
     <col customWidth="true" max="13" min="13" width="75"/>
     <col customWidth="true" max="14" min="14" width="40"/>
-    <col customWidth="true" max="15" min="15" width="40.714285714285715"/>
+    <col customWidth="true" max="15" min="15" width="42.142857142857146"/>
     <col customWidth="true" max="16" min="16" width="16.142857142857142"/>
     <col customWidth="true" max="17" min="17" width="80"/>
     <col customWidth="true" max="18" min="18" width="15.285714285714285"/>
@@ -927,64 +1081,64 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="O1" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="P1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="R1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="S1" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="T1" s="24" t="s">
         <v>6</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="K1" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="L1" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="M1" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="O1" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="T1" s="24" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2">
@@ -1134,43 +1288,43 @@
         <v>51</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J4" s="18" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="K4" s="19" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L4" s="23" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M4" s="23" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N4" s="23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O4" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="P4" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="P4" s="10" t="s">
+        <v>59</v>
       </c>
       <c r="Q4" s="19" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S4" s="17" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="T4" s="16" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -1196,43 +1350,43 @@
         <v>51</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J5" s="18" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M5" s="23" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N5" s="23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O5" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="P5" s="12" t="s">
-        <v>35</v>
+        <v>63</v>
+      </c>
+      <c r="P5" s="10" t="s">
+        <v>59</v>
       </c>
       <c r="Q5" s="19" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="R5" s="17" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S5" s="17" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="T5" s="16" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -1246,43 +1400,43 @@
         <v>47</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="E6" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="I6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="K6" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="L6" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="M6" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="N6" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="O6" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="K6" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="L6" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="M6" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="N6" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="O6" s="20" t="s">
-        <v>73</v>
-      </c>
       <c r="P6" s="10" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="Q6" s="19" t="s">
         <v>28</v>
@@ -1308,108 +1462,108 @@
         <v>47</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J7" s="18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K7" s="19" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="L7" s="23" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="M7" s="23" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="N7" s="23" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="P7" s="12" t="s">
-        <v>35</v>
+        <v>71</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>59</v>
       </c>
       <c r="Q7" s="19" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="R7" s="17" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S7" s="17" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="T7" s="16" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="8" t="s">
+      <c r="A8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K8" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="L8" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="M8" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="N8" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="O8" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="P8" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q8" s="19" t="s">
         <v>75</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K8" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="L8" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="M8" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="N8" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="O8" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="P8" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q8" s="19" t="s">
-        <v>92</v>
       </c>
       <c r="R8" s="17" t="s">
         <v>37</v>
@@ -1418,60 +1572,60 @@
         <v>38</v>
       </c>
       <c r="T8" s="16" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="I9" s="7" t="s">
+      <c r="A9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="M9" s="23" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="N9" s="23" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="O9" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="P9" s="13" t="s">
-        <v>57</v>
+        <v>78</v>
+      </c>
+      <c r="P9" s="12" t="s">
+        <v>35</v>
       </c>
       <c r="Q9" s="19" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="R9" s="17" t="s">
         <v>37</v>
@@ -1480,259 +1634,1251 @@
         <v>38</v>
       </c>
       <c r="T9" s="16" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="8" t="s">
+      <c r="A10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="K10" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="G10" s="7" t="s">
+      <c r="L10" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="H10" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="K10" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="L10" s="23" t="s">
+      <c r="M10" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="N10" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="M10" s="23" t="s">
+      <c r="O10" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="N10" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="O10" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="P10" s="13" t="s">
-        <v>57</v>
+      <c r="P10" s="10" t="s">
+        <v>59</v>
       </c>
       <c r="Q10" s="19" t="s">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="R10" s="17" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S10" s="17" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="T10" s="16" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="8" t="s">
+      <c r="A11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="G11" s="7" t="s">
+      <c r="F11" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="L11" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="H11" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J11" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="K11" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="L11" s="23" t="s">
+      <c r="M11" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="N11" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="M11" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="N11" s="23" t="s">
-        <v>90</v>
-      </c>
       <c r="O11" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="P11" s="13" t="s">
-        <v>57</v>
+        <v>93</v>
+      </c>
+      <c r="P11" s="10" t="s">
+        <v>59</v>
       </c>
       <c r="Q11" s="19" t="s">
-        <v>104</v>
+        <v>28</v>
       </c>
       <c r="R11" s="17" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S11" s="17" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="T11" s="16" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="8" t="s">
+      <c r="A12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F12" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="G12" s="7" t="s">
+      <c r="F12" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="L12" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="H12" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J12" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="K12" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="L12" s="23" t="s">
+      <c r="M12" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="N12" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="M12" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="N12" s="23" t="s">
-        <v>90</v>
-      </c>
       <c r="O12" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="P12" s="13" t="s">
-        <v>57</v>
+        <v>96</v>
+      </c>
+      <c r="P12" s="10" t="s">
+        <v>59</v>
       </c>
       <c r="Q12" s="19" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="R12" s="17" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S12" s="17" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="T12" s="16" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="8" t="s">
+      <c r="A13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="G13" s="7" t="s">
+      <c r="F13" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J13" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="K13" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="L13" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="M13" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="N13" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="O13" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="P13" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q13" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="R13" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="S13" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="T13" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="K14" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="M14" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="N14" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="O14" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="P14" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q14" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="R14" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="S14" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="T14" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J15" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="L15" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="M15" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="N15" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="O15" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="P15" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q15" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="R15" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="S15" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="T15" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="I13" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J13" s="18" t="s">
+      <c r="H16" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="K13" s="19" t="s">
+      <c r="I16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J16" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="L13" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="M13" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="N13" s="23" t="s">
+      <c r="K16" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="L16" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="M16" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="N16" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="O16" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="P16" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q16" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="R16" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="S16" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="T16" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J17" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="K17" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="L17" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="M17" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="N17" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="O17" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="P17" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q17" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="R17" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="S17" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="T17" s="16" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J18" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="K18" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="L18" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="M18" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="N18" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="O18" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="P18" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q18" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="R18" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="S18" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="T18" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J19" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="K19" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="L19" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="M19" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="N19" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="O19" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="P19" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q19" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="R19" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="S19" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="T19" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="H20" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="O13" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="P13" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q13" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="R13" s="17" t="s">
+      <c r="I20" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J20" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="K20" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="L20" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="M20" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="N20" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="O20" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="P20" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q20" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="R20" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="S20" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="T20" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="K21" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="L21" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="M21" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="N21" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="O21" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="P21" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q21" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="R21" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="S21" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="T21" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J22" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="K22" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="L22" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="M22" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="N22" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="O22" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="P22" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q22" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="R22" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="S22" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="T22" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="K23" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="L23" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="M23" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="N23" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="O23" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="P23" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q23" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="R23" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="S23" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="T23" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J24" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K24" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="L24" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="M24" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="N24" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="O24" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="P24" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q24" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="R24" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="S13" s="17" t="s">
+      <c r="S24" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="T13" s="16" t="s">
-        <v>93</v>
+      <c r="T24" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J25" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="K25" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="L25" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="M25" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="N25" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="O25" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="P25" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q25" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="R25" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="S25" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="T25" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J26" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="K26" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="L26" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="M26" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="N26" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="O26" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="P26" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q26" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="R26" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="S26" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="T26" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J27" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K27" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="L27" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="M27" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="N27" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="O27" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="P27" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q27" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="R27" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="S27" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="T27" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J28" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="K28" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="L28" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="M28" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="N28" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="O28" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="P28" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q28" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="R28" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="S28" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="T28" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J29" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="K29" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="L29" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="M29" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="N29" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="O29" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="P29" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q29" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="R29" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="S29" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="T29" s="16" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$T$13"/>
+  <autoFilter ref="$A$1:$T$29"/>
   <pageSetup orientation="landscape" paperSize="9"/>
   <headerFooter>
     <oddHeader>&amp;R&amp;P</oddHeader>

--- a/threagile/output/linddun/risks.xlsx
+++ b/threagile/output/linddun/risks.xlsx
@@ -17,66 +17,66 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="171">
+  <si>
+    <t>CWE</t>
+  </si>
+  <si>
+    <t>Identified Risk</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
   <si>
     <t>Mitigation</t>
   </si>
   <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>STRIDE</t>
+  </si>
+  <si>
+    <t>Impact</t>
+  </si>
+  <si>
+    <t>Risk Category</t>
+  </si>
+  <si>
+    <t>Communication Link</t>
+  </si>
+  <si>
+    <t>RAA %</t>
+  </si>
+  <si>
+    <t>Check</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>Ticket</t>
+  </si>
+  <si>
+    <t>Likelihood</t>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <t>Technical Asset</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
     <t>Checked by</t>
-  </si>
-  <si>
-    <t>CWE</t>
-  </si>
-  <si>
-    <t>Technical Asset</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Ticket</t>
-  </si>
-  <si>
-    <t>Likelihood</t>
-  </si>
-  <si>
-    <t>Impact</t>
-  </si>
-  <si>
-    <t>Identified Risk</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Justification</t>
-  </si>
-  <si>
-    <t>Communication Link</t>
-  </si>
-  <si>
-    <t>RAA %</t>
-  </si>
-  <si>
-    <t>Check</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>STRIDE</t>
-  </si>
-  <si>
-    <t>Severity</t>
-  </si>
-  <si>
-    <t>Function</t>
-  </si>
-  <si>
-    <t>Risk Category</t>
   </si>
   <si>
     <t>Elevated</t>
@@ -177,13 +177,7 @@
     <t>Detectability - PII Flows Without Audit Logging</t>
   </si>
   <si>
-    <t>ECS Container Platform</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>Detectability: ECS Container Platform processes PII and has communication links without audit logging</t>
+    <t>Detectability: Nginx Reverse Proxy processes PII and has communication links without audit logging</t>
   </si>
   <si>
     <t>Enable audit logging on all links carrying personal data</t>
@@ -196,51 +190,6 @@
     <t>Are all communication links that carry personal data audit-logged?</t>
   </si>
   <si>
-    <t>detecting-no-audit-logging@ecs-platform</t>
-  </si>
-  <si>
-    <t>Unchecked</t>
-  </si>
-  <si>
-    <t>LLM Note Summarizer</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>Detectability: LLM Note Summarizer processes PII and has communication links without audit logging</t>
-  </si>
-  <si>
-    <t>detecting-no-audit-logging@llm-summarizer</t>
-  </si>
-  <si>
-    <t>Lambda Email Notifier</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Detectability: Lambda Email Notifier processes PII and has communication links without audit logging</t>
-  </si>
-  <si>
-    <t>detecting-no-audit-logging@lambda-notifier</t>
-  </si>
-  <si>
-    <t>Note RAG Pipeline</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Detectability: Note RAG Pipeline processes PII and has communication links without audit logging</t>
-  </si>
-  <si>
-    <t>detecting-no-audit-logging@rag-pipeline</t>
-  </si>
-  <si>
-    <t>Detectability: Nginx Reverse Proxy processes PII and has communication links without audit logging</t>
-  </si>
-  <si>
     <t>detecting-no-audit-logging@nginx-proxy</t>
   </si>
   <si>
@@ -267,6 +216,61 @@
     <t>VAULT-116</t>
   </si>
   <si>
+    <t>ECS Container Platform</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>Detectability: ECS Container Platform processes PII and has communication links without audit logging</t>
+  </si>
+  <si>
+    <t>detecting-no-audit-logging@ecs-platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension of the structured audit-logging effort (VAULT-116) to the remaining processing components: ECS platform events, Lambda notifier, LLM summarizer, and RAG pipeline.
+</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>LLM Note Summarizer</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Detectability: LLM Note Summarizer processes PII and has communication links without audit logging</t>
+  </si>
+  <si>
+    <t>detecting-no-audit-logging@llm-summarizer</t>
+  </si>
+  <si>
+    <t>Lambda Email Notifier</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Detectability: Lambda Email Notifier processes PII and has communication links without audit logging</t>
+  </si>
+  <si>
+    <t>detecting-no-audit-logging@lambda-notifier</t>
+  </si>
+  <si>
+    <t>Note RAG Pipeline</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Detectability: Note RAG Pipeline processes PII and has communication links without audit logging</t>
+  </si>
+  <si>
+    <t>detecting-no-audit-logging@rag-pipeline</t>
+  </si>
+  <si>
     <t>CWE-312</t>
   </si>
   <si>
@@ -295,6 +299,10 @@
     <t>identifying-pii-stored-unencrypted@rds-postgresql</t>
   </si>
   <si>
+    <t xml:space="preserve">Intentional misconfiguration: encryption at rest is deliberately absent on PostgreSQL/Redis/MinIO/vector store (and disabled on RDS/S3 in the Terraform) for training purposes. Production deployments require the VAULT-110/VAULT-89 encryption work before launch.
+</t>
+  </si>
+  <si>
     <t>AWS S3 Notes Bucket</t>
   </si>
   <si>
@@ -381,6 +389,10 @@
     <t>pii-client-side-storage@browser-spa</t>
   </si>
   <si>
+    <t xml:space="preserve">The SPA keeps the JWT in memory and caches note drafts in IndexedDB to support offline editing — a deliberate product decision. Cache is cleared on logout; device-level encryption is the user's control.
+</t>
+  </si>
+  <si>
     <t>CWE-359</t>
   </si>
   <si>
@@ -419,13 +431,7 @@
     <t>Linkability - Same PII Data Asset Processed Across Multiple Trust Boundaries</t>
   </si>
   <si>
-    <t>AWS API Gateway</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>Linkability: AWS API Gateway processes a PII data asset also flowing into another trust boundary</t>
+    <t>Linkability: API Server processes a PII data asset also flowing into another trust boundary</t>
   </si>
   <si>
     <t>Apply data minimisation and per-context pseudonymisation</t>
@@ -438,42 +444,6 @@
     <t>Does each PII data asset appear in assets across more than one trust boundary?</t>
   </si>
   <si>
-    <t>linking-pii-multi-boundary@aws-api-gateway</t>
-  </si>
-  <si>
-    <t>Linkability: AWS RDS PostgreSQL processes a PII data asset also flowing into another trust boundary</t>
-  </si>
-  <si>
-    <t>linking-pii-multi-boundary@rds-postgresql</t>
-  </si>
-  <si>
-    <t>Linkability: AWS S3 Notes Bucket processes a PII data asset also flowing into another trust boundary</t>
-  </si>
-  <si>
-    <t>linking-pii-multi-boundary@s3-notes-bucket</t>
-  </si>
-  <si>
-    <t>Linkability: ECS Container Platform processes a PII data asset also flowing into another trust boundary</t>
-  </si>
-  <si>
-    <t>linking-pii-multi-boundary@ecs-platform</t>
-  </si>
-  <si>
-    <t>Linkability: Note RAG Pipeline processes a PII data asset also flowing into another trust boundary</t>
-  </si>
-  <si>
-    <t>linking-pii-multi-boundary@rag-pipeline</t>
-  </si>
-  <si>
-    <t>Linkability: VaultNote Vector Store processes a PII data asset also flowing into another trust boundary</t>
-  </si>
-  <si>
-    <t>linking-pii-multi-boundary@vector-store</t>
-  </si>
-  <si>
-    <t>Linkability: API Server processes a PII data asset also flowing into another trust boundary</t>
-  </si>
-  <si>
     <t>linking-pii-multi-boundary@api-server</t>
   </si>
   <si>
@@ -532,6 +502,55 @@
   <si>
     <t xml:space="preserve">Session identifiers originate from users across the Internet boundary. Storage in Redis within the Data Tier is unavoidable. Mitigated by short TTL (15 minutes), revocation list, and password-protected access.
 </t>
+  </si>
+  <si>
+    <t>AWS API Gateway</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Linkability: AWS API Gateway processes a PII data asset also flowing into another trust boundary</t>
+  </si>
+  <si>
+    <t>linking-pii-multi-boundary@aws-api-gateway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data-flow minimization review for the remaining PII-crossing assets (API Gateway, ECS, RAG pipeline, RDS, S3, vector store): pseudonymous user IDs in AI-service calls and embedding metadata.
+</t>
+  </si>
+  <si>
+    <t>VAULT-157</t>
+  </si>
+  <si>
+    <t>Linkability: AWS RDS PostgreSQL processes a PII data asset also flowing into another trust boundary</t>
+  </si>
+  <si>
+    <t>linking-pii-multi-boundary@rds-postgresql</t>
+  </si>
+  <si>
+    <t>Linkability: AWS S3 Notes Bucket processes a PII data asset also flowing into another trust boundary</t>
+  </si>
+  <si>
+    <t>linking-pii-multi-boundary@s3-notes-bucket</t>
+  </si>
+  <si>
+    <t>Linkability: ECS Container Platform processes a PII data asset also flowing into another trust boundary</t>
+  </si>
+  <si>
+    <t>linking-pii-multi-boundary@ecs-platform</t>
+  </si>
+  <si>
+    <t>Linkability: Note RAG Pipeline processes a PII data asset also flowing into another trust boundary</t>
+  </si>
+  <si>
+    <t>linking-pii-multi-boundary@rag-pipeline</t>
+  </si>
+  <si>
+    <t>Linkability: VaultNote Vector Store processes a PII data asset also flowing into another trust boundary</t>
+  </si>
+  <si>
+    <t>linking-pii-multi-boundary@vector-store</t>
   </si>
 </sst>
 </file>
@@ -540,149 +559,127 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <fonts count="23">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
+      <family val="2"/>
       <b val="1"/>
+      <color rgb="FFFF2600"/>
       <sz val="12"/>
-      <color rgb="FFFF2600"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FFFF2600"/>
       <sz val="12"/>
-      <color rgb="FFFF2600"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
       <b val="1"/>
+      <color rgb="FFA0281E"/>
       <sz val="12"/>
-      <color rgb="FFA0281E"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FFA0281E"/>
       <sz val="12"/>
-      <color rgb="FFA0281E"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
       <b val="1"/>
+      <color rgb="FFFF8E00"/>
       <sz val="12"/>
-      <color rgb="FFFF8E00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FFFF8E00"/>
       <sz val="12"/>
-      <color rgb="FFFF8E00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
       <b val="1"/>
+      <color rgb="FFC87832"/>
       <sz val="12"/>
-      <color rgb="FFC87832"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FFC87832"/>
       <sz val="12"/>
-      <color rgb="FFC87832"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
       <b val="1"/>
+      <color rgb="FF23465F"/>
       <sz val="12"/>
-      <color rgb="FF23465F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FF23465F"/>
       <sz val="12"/>
-      <color rgb="FF23465F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FF008F00"/>
       <sz val="12"/>
-      <color rgb="FF008F00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FF0000FF"/>
       <sz val="12"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FFFF40FF"/>
       <sz val="12"/>
-      <color rgb="FFFF40FF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FFFF9300"/>
       <sz val="12"/>
-      <color rgb="FFFF9300"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FF666666"/>
       <sz val="12"/>
-      <color rgb="FF666666"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FF7F7F7F"/>
       <sz val="10"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
       <b val="1"/>
+      <color rgb="FF000000"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FF008F00"/>
       <sz val="10"/>
-      <color rgb="FF008F00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
       <b val="1"/>
+      <color rgb="FF000000"/>
       <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1081,64 +1078,64 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="24" t="s">
+      <c r="I1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="24" t="s">
+      <c r="J1" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="24" t="s">
+      <c r="P1" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q1" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="R1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="S1" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="24" t="s">
+      <c r="T1" s="24" t="s">
         <v>14</v>
-      </c>
-      <c r="O1" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="P1" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q1" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="R1" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="S1" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="T1" s="24" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2">
@@ -1288,43 +1285,43 @@
         <v>51</v>
       </c>
       <c r="H4" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="18" t="s">
+      <c r="L4" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="K4" s="19" t="s">
+      <c r="M4" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="L4" s="23" t="s">
+      <c r="N4" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="M4" s="23" t="s">
+      <c r="O4" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="N4" s="23" t="s">
+      <c r="P4" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="O4" s="20" t="s">
+      <c r="Q4" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="P4" s="10" t="s">
+      <c r="R4" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="S4" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="T4" s="16" t="s">
         <v>59</v>
-      </c>
-      <c r="Q4" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="R4" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="S4" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="T4" s="16" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -1350,43 +1347,43 @@
         <v>51</v>
       </c>
       <c r="H5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J5" s="18" t="s">
+      <c r="L5" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="M5" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="N5" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="O5" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="K5" s="19" t="s">
+      <c r="P5" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q5" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="L5" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="M5" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="N5" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="O5" s="20" t="s">
+      <c r="R5" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="S5" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="T5" s="16" t="s">
         <v>63</v>
-      </c>
-      <c r="P5" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q5" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="R5" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="S5" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="T5" s="16" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -1424,31 +1421,31 @@
         <v>66</v>
       </c>
       <c r="L6" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="M6" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="N6" s="23" t="s">
         <v>55</v>
-      </c>
-      <c r="M6" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="N6" s="23" t="s">
-        <v>57</v>
       </c>
       <c r="O6" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="P6" s="10" t="s">
-        <v>59</v>
+      <c r="P6" s="12" t="s">
+        <v>35</v>
       </c>
       <c r="Q6" s="19" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="R6" s="17" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="S6" s="17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T6" s="16" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7">
@@ -1474,43 +1471,43 @@
         <v>51</v>
       </c>
       <c r="H7" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="L7" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="M7" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="N7" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="O7" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="P7" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q7" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J7" s="18" t="s">
+      <c r="R7" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="K7" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="L7" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="M7" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="N7" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="O7" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="P7" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q7" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="R7" s="17" t="s">
-        <v>28</v>
-      </c>
       <c r="S7" s="17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T7" s="16" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8">
@@ -1536,43 +1533,43 @@
         <v>51</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J8" s="18" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="K8" s="19" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="L8" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="M8" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="N8" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="M8" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="N8" s="23" t="s">
-        <v>57</v>
-      </c>
       <c r="O8" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="P8" s="13" t="s">
-        <v>74</v>
+        <v>77</v>
+      </c>
+      <c r="P8" s="12" t="s">
+        <v>35</v>
       </c>
       <c r="Q8" s="19" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="R8" s="17" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="S8" s="17" t="s">
         <v>38</v>
       </c>
       <c r="T8" s="16" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9">
@@ -1598,43 +1595,43 @@
         <v>51</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L9" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="M9" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="N9" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="M9" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="N9" s="23" t="s">
-        <v>57</v>
-      </c>
       <c r="O9" s="20" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="P9" s="12" t="s">
         <v>35</v>
       </c>
       <c r="Q9" s="19" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="R9" s="17" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="S9" s="17" t="s">
         <v>38</v>
       </c>
       <c r="T9" s="16" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
@@ -1654,46 +1651,46 @@
         <v>24</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J10" s="18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K10" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M10" s="23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N10" s="23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O10" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="P10" s="10" t="s">
-        <v>59</v>
+        <v>90</v>
+      </c>
+      <c r="P10" s="13" t="s">
+        <v>57</v>
       </c>
       <c r="Q10" s="19" t="s">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="R10" s="17" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="S10" s="17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T10" s="16" t="s">
         <v>28</v>
@@ -1716,46 +1713,46 @@
         <v>24</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J11" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="L11" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="M11" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="N11" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="O11" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="P11" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q11" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="K11" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="L11" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="M11" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="N11" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="O11" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="P11" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q11" s="19" t="s">
-        <v>28</v>
-      </c>
       <c r="R11" s="17" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="S11" s="17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T11" s="16" t="s">
         <v>28</v>
@@ -1778,46 +1775,46 @@
         <v>24</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J12" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="L12" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="M12" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="N12" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="O12" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="P12" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q12" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="K12" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="L12" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="M12" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="N12" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="O12" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="P12" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q12" s="19" t="s">
-        <v>28</v>
-      </c>
       <c r="R12" s="17" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="S12" s="17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T12" s="16" t="s">
         <v>28</v>
@@ -1840,46 +1837,46 @@
         <v>24</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J13" s="18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K13" s="19" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L13" s="23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M13" s="23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N13" s="23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O13" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="P13" s="10" t="s">
-        <v>59</v>
+        <v>101</v>
+      </c>
+      <c r="P13" s="13" t="s">
+        <v>57</v>
       </c>
       <c r="Q13" s="19" t="s">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="R13" s="17" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="S13" s="17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T13" s="16" t="s">
         <v>28</v>
@@ -1902,46 +1899,46 @@
         <v>24</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K14" s="19" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L14" s="23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M14" s="23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N14" s="23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O14" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="P14" s="10" t="s">
-        <v>59</v>
+        <v>105</v>
+      </c>
+      <c r="P14" s="13" t="s">
+        <v>57</v>
       </c>
       <c r="Q14" s="19" t="s">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="R14" s="17" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="S14" s="17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T14" s="16" t="s">
         <v>28</v>
@@ -1964,46 +1961,46 @@
         <v>24</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J15" s="18" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K15" s="19" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L15" s="23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M15" s="23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N15" s="23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O15" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="P15" s="10" t="s">
-        <v>59</v>
+        <v>109</v>
+      </c>
+      <c r="P15" s="13" t="s">
+        <v>57</v>
       </c>
       <c r="Q15" s="19" t="s">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="R15" s="17" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="S15" s="17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T15" s="16" t="s">
         <v>28</v>
@@ -2023,49 +2020,49 @@
         <v>23</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K16" s="19" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="L16" s="23" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="M16" s="23" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="N16" s="23" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="O16" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="P16" s="10" t="s">
-        <v>59</v>
+        <v>119</v>
+      </c>
+      <c r="P16" s="13" t="s">
+        <v>57</v>
       </c>
       <c r="Q16" s="19" t="s">
-        <v>28</v>
+        <v>120</v>
       </c>
       <c r="R16" s="17" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="S16" s="17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T16" s="16" t="s">
         <v>28</v>
@@ -2088,49 +2085,49 @@
         <v>24</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K17" s="19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="L17" s="23" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M17" s="23" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="N17" s="23" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O17" s="20" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="P17" s="12" t="s">
         <v>35</v>
       </c>
       <c r="Q17" s="19" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="R17" s="17" t="s">
         <v>37</v>
       </c>
       <c r="S17" s="17" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="T17" s="16" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18">
@@ -2138,7 +2135,7 @@
         <v>47</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>47</v>
@@ -2150,49 +2147,49 @@
         <v>24</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>130</v>
+        <v>27</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>28</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>131</v>
+        <v>29</v>
       </c>
       <c r="K18" s="19" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L18" s="23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M18" s="23" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N18" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O18" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="P18" s="10" t="s">
-        <v>59</v>
+        <v>137</v>
+      </c>
+      <c r="P18" s="13" t="s">
+        <v>57</v>
       </c>
       <c r="Q18" s="19" t="s">
-        <v>28</v>
+        <v>138</v>
       </c>
       <c r="R18" s="17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S18" s="17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T18" s="16" t="s">
-        <v>28</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19">
@@ -2200,7 +2197,7 @@
         <v>47</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>47</v>
@@ -2212,49 +2209,49 @@
         <v>24</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>28</v>
       </c>
       <c r="J19" s="18" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="K19" s="19" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="L19" s="23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M19" s="23" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N19" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O19" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="P19" s="10" t="s">
-        <v>59</v>
+        <v>141</v>
+      </c>
+      <c r="P19" s="13" t="s">
+        <v>57</v>
       </c>
       <c r="Q19" s="19" t="s">
-        <v>28</v>
+        <v>142</v>
       </c>
       <c r="R19" s="17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S19" s="17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T19" s="16" t="s">
-        <v>28</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20">
@@ -2262,7 +2259,7 @@
         <v>47</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>47</v>
@@ -2274,49 +2271,49 @@
         <v>24</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>28</v>
       </c>
       <c r="J20" s="18" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K20" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="L20" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="M20" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="N20" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="O20" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="P20" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q20" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="R20" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="S20" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="T20" s="16" t="s">
         <v>139</v>
-      </c>
-      <c r="L20" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="M20" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="N20" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="O20" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="P20" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q20" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="R20" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="S20" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="T20" s="16" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="21">
@@ -2324,7 +2321,7 @@
         <v>47</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>47</v>
@@ -2336,49 +2333,49 @@
         <v>24</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>28</v>
       </c>
       <c r="J21" s="18" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="K21" s="19" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="L21" s="23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M21" s="23" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N21" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O21" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="P21" s="10" t="s">
-        <v>59</v>
+        <v>147</v>
+      </c>
+      <c r="P21" s="13" t="s">
+        <v>57</v>
       </c>
       <c r="Q21" s="19" t="s">
-        <v>28</v>
+        <v>148</v>
       </c>
       <c r="R21" s="17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S21" s="17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T21" s="16" t="s">
-        <v>28</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22">
@@ -2386,7 +2383,7 @@
         <v>47</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>47</v>
@@ -2398,49 +2395,49 @@
         <v>24</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>28</v>
       </c>
       <c r="J22" s="18" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="K22" s="19" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="L22" s="23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M22" s="23" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N22" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O22" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="P22" s="10" t="s">
-        <v>59</v>
+        <v>150</v>
+      </c>
+      <c r="P22" s="13" t="s">
+        <v>57</v>
       </c>
       <c r="Q22" s="19" t="s">
-        <v>28</v>
+        <v>151</v>
       </c>
       <c r="R22" s="17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S22" s="17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T22" s="16" t="s">
-        <v>28</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23">
@@ -2448,7 +2445,7 @@
         <v>47</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>47</v>
@@ -2460,49 +2457,49 @@
         <v>24</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>28</v>
       </c>
       <c r="J23" s="18" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K23" s="19" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="L23" s="23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M23" s="23" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N23" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O23" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="P23" s="10" t="s">
-        <v>59</v>
+        <v>153</v>
+      </c>
+      <c r="P23" s="13" t="s">
+        <v>57</v>
       </c>
       <c r="Q23" s="19" t="s">
-        <v>28</v>
+        <v>154</v>
       </c>
       <c r="R23" s="17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S23" s="17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T23" s="16" t="s">
-        <v>28</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24">
@@ -2510,7 +2507,7 @@
         <v>47</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>47</v>
@@ -2522,49 +2519,49 @@
         <v>24</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>27</v>
+        <v>155</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>28</v>
       </c>
       <c r="J24" s="18" t="s">
-        <v>29</v>
+        <v>156</v>
       </c>
       <c r="K24" s="19" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="L24" s="23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M24" s="23" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N24" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O24" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="P24" s="13" t="s">
-        <v>74</v>
+        <v>158</v>
+      </c>
+      <c r="P24" s="12" t="s">
+        <v>35</v>
       </c>
       <c r="Q24" s="19" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="R24" s="17" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="S24" s="17" t="s">
         <v>38</v>
       </c>
       <c r="T24" s="16" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25">
@@ -2572,7 +2569,7 @@
         <v>47</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>47</v>
@@ -2584,49 +2581,49 @@
         <v>24</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="I25" s="7" t="s">
         <v>28</v>
       </c>
       <c r="J25" s="18" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="K25" s="19" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="L25" s="23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M25" s="23" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N25" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O25" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="P25" s="13" t="s">
-        <v>74</v>
+        <v>162</v>
+      </c>
+      <c r="P25" s="12" t="s">
+        <v>35</v>
       </c>
       <c r="Q25" s="19" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="R25" s="17" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="S25" s="17" t="s">
         <v>38</v>
       </c>
       <c r="T25" s="16" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26">
@@ -2634,7 +2631,7 @@
         <v>47</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>47</v>
@@ -2646,49 +2643,49 @@
         <v>24</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>28</v>
       </c>
       <c r="J26" s="18" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K26" s="19" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="L26" s="23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M26" s="23" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N26" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O26" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="P26" s="13" t="s">
-        <v>74</v>
+        <v>164</v>
+      </c>
+      <c r="P26" s="12" t="s">
+        <v>35</v>
       </c>
       <c r="Q26" s="19" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="R26" s="17" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="S26" s="17" t="s">
         <v>38</v>
       </c>
       <c r="T26" s="16" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27">
@@ -2696,7 +2693,7 @@
         <v>47</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>47</v>
@@ -2708,49 +2705,49 @@
         <v>24</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="I27" s="7" t="s">
         <v>28</v>
       </c>
       <c r="J27" s="18" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="K27" s="19" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="L27" s="23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M27" s="23" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N27" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O27" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="P27" s="13" t="s">
-        <v>74</v>
+        <v>166</v>
+      </c>
+      <c r="P27" s="12" t="s">
+        <v>35</v>
       </c>
       <c r="Q27" s="19" t="s">
         <v>159</v>
       </c>
       <c r="R27" s="17" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="S27" s="17" t="s">
         <v>38</v>
       </c>
       <c r="T27" s="16" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28">
@@ -2758,7 +2755,7 @@
         <v>47</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>47</v>
@@ -2770,49 +2767,49 @@
         <v>24</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="I28" s="7" t="s">
         <v>28</v>
       </c>
       <c r="J28" s="18" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="K28" s="19" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="L28" s="23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M28" s="23" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N28" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O28" s="20" t="s">
-        <v>161</v>
-      </c>
-      <c r="P28" s="13" t="s">
-        <v>74</v>
+        <v>168</v>
+      </c>
+      <c r="P28" s="12" t="s">
+        <v>35</v>
       </c>
       <c r="Q28" s="19" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="R28" s="17" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="S28" s="17" t="s">
         <v>38</v>
       </c>
       <c r="T28" s="16" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29">
@@ -2820,7 +2817,7 @@
         <v>47</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>47</v>
@@ -2832,49 +2829,49 @@
         <v>24</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="I29" s="7" t="s">
         <v>28</v>
       </c>
       <c r="J29" s="18" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="K29" s="19" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="L29" s="23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M29" s="23" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N29" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O29" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="P29" s="13" t="s">
-        <v>74</v>
+        <v>170</v>
+      </c>
+      <c r="P29" s="12" t="s">
+        <v>35</v>
       </c>
       <c r="Q29" s="19" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="R29" s="17" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="S29" s="17" t="s">
         <v>38</v>
       </c>
       <c r="T29" s="16" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
